--- a/Admin/Content/Files/Template_ImportSanPham.xlsx
+++ b/Admin/Content/Files/Template_ImportSanPham.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\admin\Downloads\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\DATN\Web\Admin\Content\Files\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{282413CD-8CC0-4285-89E9-958F45DDC0DB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{89E65B55-14C1-4FA4-BAEA-8AC6F18706D0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -20,136 +20,46 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="41" uniqueCount="41">
-  <si>
-    <t>CategoryName</t>
-  </si>
-  <si>
-    <t>Name</t>
-  </si>
-  <si>
-    <t>Slug</t>
-  </si>
-  <si>
-    <t>Description</t>
-  </si>
-  <si>
-    <t>Price</t>
-  </si>
-  <si>
-    <t>SalePrice</t>
-  </si>
-  <si>
-    <t>Image</t>
-  </si>
-  <si>
-    <t>Quantity</t>
-  </si>
-  <si>
-    <t>IsActive</t>
-  </si>
-  <si>
-    <t>IsFeatured</t>
-  </si>
-  <si>
-    <t>Tags</t>
-  </si>
-  <si>
-    <t>Sữa rửa mặt</t>
-  </si>
-  <si>
-    <t>Kem chống nắng</t>
-  </si>
-  <si>
-    <t>Serum</t>
-  </si>
-  <si>
-    <t>Kem dưỡng</t>
-  </si>
-  <si>
-    <t>Mặt nạ</t>
-  </si>
-  <si>
-    <t>Sữa rửa mặt trà xanh</t>
-  </si>
-  <si>
-    <t>Kem chống nắng SPF50</t>
-  </si>
-  <si>
-    <t>Serum Vitamin C</t>
-  </si>
-  <si>
-    <t>Kem dưỡng ẩm ban đêm</t>
-  </si>
-  <si>
-    <t>Mặt nạ đất sét</t>
-  </si>
-  <si>
-    <t>sua-rua-mat-tra-xanh</t>
-  </si>
-  <si>
-    <t>kem-chong-nang-spf50</t>
-  </si>
-  <si>
-    <t>serum-vitamin-c</t>
-  </si>
-  <si>
-    <t>kem-duong-am-ban-dem</t>
-  </si>
-  <si>
-    <t>mat-na-dat-set</t>
-  </si>
-  <si>
-    <t>Làm sạch dịu nhẹ, ngừa mụn</t>
-  </si>
-  <si>
-    <t>Bảo vệ da khỏi UVB/UVA</t>
-  </si>
-  <si>
-    <t>Giúp làm sáng da, mờ thâm</t>
-  </si>
-  <si>
-    <t>Dưỡng ẩm chuyên sâu cho da khô</t>
-  </si>
-  <si>
-    <t>Làm sạch sâu lỗ chân lông</t>
-  </si>
-  <si>
-    <t>sua-rua-mat.jpg</t>
-  </si>
-  <si>
-    <t>kem-chong-nang.jpg</t>
-  </si>
-  <si>
-    <t>serum-vitamin-c.jpg</t>
-  </si>
-  <si>
-    <t>kem-duong-am.jpg</t>
-  </si>
-  <si>
-    <t>mat-na-dat-set.jpg</t>
-  </si>
-  <si>
-    <t>sua-rua-mat,tra-xanh</t>
-  </si>
-  <si>
-    <t>chong-nang,spf50</t>
-  </si>
-  <si>
-    <t>serum,vitamin-c,chong-lao-hoa</t>
-  </si>
-  <si>
-    <t>duong-am,ban-dem,da-kho</t>
-  </si>
-  <si>
-    <t>mat-na,dat-set,lam-sach</t>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="11" uniqueCount="11">
+  <si>
+    <t>TenThuoc</t>
+  </si>
+  <si>
+    <t>HoatChat</t>
+  </si>
+  <si>
+    <t>DonViTinh</t>
+  </si>
+  <si>
+    <t>QuyCach</t>
+  </si>
+  <si>
+    <t>GiaBan</t>
+  </si>
+  <si>
+    <t>SoLuong</t>
+  </si>
+  <si>
+    <t>HinhAnh</t>
+  </si>
+  <si>
+    <t>KichHoat</t>
+  </si>
+  <si>
+    <t>NhaCungCapId</t>
+  </si>
+  <si>
+    <t>DanhMucId</t>
+  </si>
+  <si>
+    <t>GiaGoc</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="2" x14ac:knownFonts="1">
+  <fonts count="3" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -164,6 +74,13 @@
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color theme="10"/>
+      <name val="Calibri"/>
+      <family val="2"/>
     </font>
   </fonts>
   <fills count="2">
@@ -198,16 +115,22 @@
       <diagonal/>
     </border>
   </borders>
-  <cellStyleXfs count="1">
+  <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="top"/>
+      <protection locked="0"/>
+    </xf>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="1" applyAlignment="1" applyProtection="1"/>
   </cellXfs>
-  <cellStyles count="1">
+  <cellStyles count="2">
+    <cellStyle name="Hyperlink" xfId="1" builtinId="8"/>
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
@@ -510,222 +433,61 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:K6"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <dimension ref="A1:K4"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="7" max="7" width="28.109375" customWidth="1"/>
-    <col min="11" max="11" width="27.5546875" customWidth="1"/>
+    <col min="1" max="1" width="14.42578125" customWidth="1"/>
+    <col min="2" max="2" width="17.7109375" customWidth="1"/>
+    <col min="3" max="3" width="21.85546875" customWidth="1"/>
+    <col min="4" max="4" width="22.7109375" customWidth="1"/>
+    <col min="5" max="5" width="19" customWidth="1"/>
+    <col min="6" max="7" width="20.7109375" customWidth="1"/>
+    <col min="10" max="10" width="49.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="C1" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="1" t="s">
+      <c r="D1" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="1" t="s">
+      <c r="E1" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="1" t="s">
+      <c r="F1" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="1" t="s">
+      <c r="G1" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="H1" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="1" t="s">
+      <c r="I1" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="G1" s="1" t="s">
+      <c r="J1" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="H1" s="1" t="s">
+      <c r="K1" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="I1" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="J1" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="K1" s="1" t="s">
-        <v>10</v>
-      </c>
     </row>
-    <row r="2" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A2" t="s">
-        <v>11</v>
-      </c>
-      <c r="B2" t="s">
-        <v>16</v>
-      </c>
-      <c r="C2" t="s">
-        <v>21</v>
-      </c>
-      <c r="D2" t="s">
-        <v>26</v>
-      </c>
-      <c r="E2">
-        <v>150000</v>
-      </c>
-      <c r="F2">
-        <v>120000</v>
-      </c>
-      <c r="G2" t="s">
-        <v>31</v>
-      </c>
-      <c r="H2">
-        <v>100</v>
-      </c>
-      <c r="I2" t="b">
-        <v>1</v>
-      </c>
-      <c r="J2" t="b">
-        <v>1</v>
-      </c>
-      <c r="K2" t="s">
-        <v>36</v>
-      </c>
+    <row r="2" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="J2" s="2"/>
     </row>
-    <row r="3" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A3" t="s">
-        <v>12</v>
-      </c>
-      <c r="B3" t="s">
-        <v>17</v>
-      </c>
-      <c r="C3" t="s">
-        <v>22</v>
-      </c>
-      <c r="D3" t="s">
-        <v>27</v>
-      </c>
-      <c r="E3">
-        <v>250000</v>
-      </c>
-      <c r="F3">
-        <v>200000</v>
-      </c>
-      <c r="G3" t="s">
-        <v>32</v>
-      </c>
-      <c r="H3">
-        <v>200</v>
-      </c>
-      <c r="I3" t="b">
-        <v>1</v>
-      </c>
-      <c r="J3" t="b">
-        <v>0</v>
-      </c>
-      <c r="K3" t="s">
-        <v>37</v>
-      </c>
+    <row r="3" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="J3" s="2"/>
     </row>
-    <row r="4" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A4" t="s">
-        <v>13</v>
-      </c>
-      <c r="B4" t="s">
-        <v>18</v>
-      </c>
-      <c r="C4" t="s">
-        <v>23</v>
-      </c>
-      <c r="D4" t="s">
-        <v>28</v>
-      </c>
-      <c r="E4">
-        <v>320000</v>
-      </c>
-      <c r="F4">
-        <v>290000</v>
-      </c>
-      <c r="G4" t="s">
-        <v>33</v>
-      </c>
-      <c r="H4">
-        <v>150</v>
-      </c>
-      <c r="I4" t="b">
-        <v>1</v>
-      </c>
-      <c r="J4" t="b">
-        <v>1</v>
-      </c>
-      <c r="K4" t="s">
-        <v>38</v>
-      </c>
-    </row>
-    <row r="5" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A5" t="s">
-        <v>14</v>
-      </c>
-      <c r="B5" t="s">
-        <v>19</v>
-      </c>
-      <c r="C5" t="s">
-        <v>24</v>
-      </c>
-      <c r="D5" t="s">
-        <v>29</v>
-      </c>
-      <c r="E5">
-        <v>280000</v>
-      </c>
-      <c r="F5">
-        <v>250000</v>
-      </c>
-      <c r="G5" t="s">
-        <v>34</v>
-      </c>
-      <c r="H5">
-        <v>180</v>
-      </c>
-      <c r="I5" t="b">
-        <v>1</v>
-      </c>
-      <c r="J5" t="b">
-        <v>0</v>
-      </c>
-      <c r="K5" t="s">
-        <v>39</v>
-      </c>
-    </row>
-    <row r="6" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A6" t="s">
-        <v>15</v>
-      </c>
-      <c r="B6" t="s">
-        <v>20</v>
-      </c>
-      <c r="C6" t="s">
-        <v>25</v>
-      </c>
-      <c r="D6" t="s">
-        <v>30</v>
-      </c>
-      <c r="E6">
-        <v>180000</v>
-      </c>
-      <c r="F6">
-        <v>160000</v>
-      </c>
-      <c r="G6" t="s">
-        <v>35</v>
-      </c>
-      <c r="H6">
-        <v>120</v>
-      </c>
-      <c r="I6" t="b">
-        <v>1</v>
-      </c>
-      <c r="J6" t="b">
-        <v>0</v>
-      </c>
-      <c r="K6" t="s">
-        <v>40</v>
-      </c>
+    <row r="4" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="J4" s="2"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/Admin/Content/Files/Template_ImportSanPham.xlsx
+++ b/Admin/Content/Files/Template_ImportSanPham.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\DATN\Web\Admin\Content\Files\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{89E65B55-14C1-4FA4-BAEA-8AC6F18706D0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C1A9A3EB-AA4B-4A84-B842-0A3FDE663C20}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="11" uniqueCount="11">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="12" uniqueCount="12">
   <si>
     <t>TenThuoc</t>
   </si>
@@ -53,6 +53,9 @@
   </si>
   <si>
     <t>GiaGoc</t>
+  </si>
+  <si>
+    <t>ThuocKeDon</t>
   </si>
 </sst>
 </file>
@@ -83,12 +86,18 @@
       <family val="2"/>
     </font>
   </fonts>
-  <fills count="2">
+  <fills count="3">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="0" tint="-0.14999847407452621"/>
+        <bgColor indexed="64"/>
+      </patternFill>
     </fill>
   </fills>
   <borders count="2">
@@ -122,12 +131,15 @@
       <protection locked="0"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="1" applyAlignment="1" applyProtection="1"/>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="1" applyAlignment="1" applyProtection="1"/>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Hyperlink" xfId="1" builtinId="8"/>
@@ -433,7 +445,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:K4"/>
+  <dimension ref="A1:L4"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="14.42578125" customWidth="1"/>
@@ -443,51 +455,56 @@
     <col min="5" max="5" width="19" customWidth="1"/>
     <col min="6" max="7" width="20.7109375" customWidth="1"/>
     <col min="10" max="10" width="49.7109375" customWidth="1"/>
+    <col min="11" max="11" width="13.140625" customWidth="1"/>
+    <col min="12" max="12" width="15.140625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A1" s="1" t="s">
+    <row r="1" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A1" s="2" t="s">
         <v>9</v>
       </c>
-      <c r="B1" s="1" t="s">
+      <c r="B1" s="2" t="s">
         <v>8</v>
       </c>
-      <c r="C1" s="1" t="s">
+      <c r="C1" s="2" t="s">
         <v>0</v>
       </c>
-      <c r="D1" s="1" t="s">
+      <c r="D1" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="E1" s="1" t="s">
+      <c r="E1" s="2" t="s">
         <v>2</v>
       </c>
-      <c r="F1" s="1" t="s">
+      <c r="F1" s="2" t="s">
         <v>3</v>
       </c>
-      <c r="G1" s="1" t="s">
+      <c r="G1" s="2" t="s">
         <v>10</v>
       </c>
-      <c r="H1" s="1" t="s">
+      <c r="H1" s="2" t="s">
         <v>4</v>
       </c>
-      <c r="I1" s="1" t="s">
+      <c r="I1" s="2" t="s">
         <v>5</v>
       </c>
-      <c r="J1" s="1" t="s">
+      <c r="J1" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="K1" s="1" t="s">
+      <c r="K1" s="2" t="s">
         <v>7</v>
       </c>
+      <c r="L1" s="3" t="s">
+        <v>11</v>
+      </c>
     </row>
-    <row r="2" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="J2" s="2"/>
+    <row r="2" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="J2" s="1"/>
     </row>
-    <row r="3" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="J3" s="2"/>
+    <row r="3" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="J3" s="1"/>
     </row>
-    <row r="4" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="J4" s="2"/>
+    <row r="4" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="J4" s="1"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
